--- a/planos_empresas/plano_empresa_20571.xlsx
+++ b/planos_empresas/plano_empresa_20571.xlsx
@@ -413,9 +413,550 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>010301 - Processamento de dados, textos, imagens, vídeos, páginas eletrônicas, aplicativos e sistemas de info</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>010302 - Armazenamento ou hospedagem de dados, textos, imagens, vídeos, páginas eletrônicas, aplicativos e sistemas de informação, entre outros formatos, e congêneres.</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>010501 - 01.05 - Licenciamento ou cessão de direito de uso de programas de computação.</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>010601 - Assessoria e consultoria em informática.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>010701 - Suporte técnico em informática, inclusive instalação, configuração e manutenção de programas de computação e bancos de dados.</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>042301 - Outros planos de saúde que se cumpram através de serviços de terceiros contratados, credenciados, cooperados ou apenas pagos pelo operador do plano mediante indicação do beneficiário.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>070101 - Engenharia e congêneres.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>070102 - Agronomia e congêneres.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>070104 - Arquitetura, urbanismo e congêneres.</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>070106 - Paisagismo e congêneres.</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>070201 - Execução, por administração, de obras de construção civil, hidráulica ou elétrica e de outras obras semelhantes, inclusive sondagem, perfuração de poços, escavação, drenagem e irrigação, terraplanagem, pavimentação, concretagem e a instalação e montagem de produtos, peças e equipamentos (exceto o fornecimento de mercadorias produzidas pelo prestador de serviços fora do local da prestação dos serviços, que fica sujeito ao ICMS).</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>070202 - Execução, por empreitada ou subempreitada, de obras de construção civil, hidráulica ou elétrica e de outras obras semelhantes, inclusive sondagem, perfuração de poços, escavação, drenagem e irrigação, terraplanagem, pavimentação, concretagem e a instalação e montagem de produtos, peças e equipamentos (exceto o fornecimento de mercadorias produzidas pelo prestador de serviços fora do local da prestação dos serviços, que fica sujeito ao ICMS).</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>070301 - Elaboração de planos diretores, estudos de viabilidade, estudos organizacionais e outros, relacionados com obras e serviços de engenharia.</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>070302 - Elaboração de anteprojetos, projetos básicos e projetos executivos para trabalhos de engenharia.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>071101 - Decoração.</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>071901 - Acompanhamento e fiscalização da execução de obras de engenharia, arquitetura e urbanismo.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>072003 - Levantamentos topográficos e congêneres.</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>080201 - Instrução, treinamento, orientação pedagógica e educacional, avaliação de conhecimentos de qualquer natureza.</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>100501 - Agenciamento, corretagem ou intermediação de bens móveis ou imóveis, não abrangidos em outros itens</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>130301 - Fotografia e cinematografia, inclusive revelação, ampliação, cópia, reprodução, trucagem e congêneres.</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>140101 - Lubrificação, limpeza, lustração, revisão, carga e recarga, conserto, restauração, blindagem, manutenção e conservação de máquinas, veículos, aparelhos, equipamentos, motores, elevadores ou de qualquer objeto (exceto peças e partes empregadas, que ficam sujeitas ao ICMS).</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>140201 - Assistência técnica.</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>170101 - Assessoria ou consultoria de qualquer natureza, não contida em outros itens desta lista.</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>170102 - Análise, exame, pesquisa, coleta, compilação e fornecimento de dados e informações de qualquer natureza, inclusive cadastro e similares.</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>170201 - Datilografia, digitação, estenografia e congêneres.</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>170202 - Expediente, secretaria em geral, apoio e infra-estrutura administrativa e congêneres.</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>170303 - Planejamento, coordenação, programação ou organização administrativa.</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>170601 - Propaganda e publicidade, inclusive promoção de vendas, planejamento de campanhas ou sistemas de publicidade, elaboração de desenhos, textos e demais materiais publicitários.</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>171201 - Administração em geral, inclusive de bens e negócios de terceiros.</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>171401 - Advocacia</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>171901 - Contabilidade, inclusive serviços técnicos e auxiliares.</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>172001 - Consultoria e assessoria econômica ou financeira.</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>230101 - Serviços de programação e comunicação visual e congêneres.</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>230102 - Serviços de desenho industrial e congêneres.</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>320101 - Serviços de desenhos técnicos.</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>370101 - Serviços de artistas, atletas, modelos e manequins.</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/planos_empresas/plano_empresa_20571.xlsx
+++ b/planos_empresas/plano_empresa_20571.xlsx
@@ -422,7 +422,11 @@
           <t>010301 - Processamento de dados, textos, imagens, vídeos, páginas eletrônicas, aplicativos e sistemas de info</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
       <c r="C1" t="inlineStr"/>
       <c r="D1" t="inlineStr">
         <is>
@@ -437,7 +441,11 @@
           <t>010302 - Armazenamento ou hospedagem de dados, textos, imagens, vídeos, páginas eletrônicas, aplicativos e sistemas de informação, entre outros formatos, e congêneres.</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>3353</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
@@ -452,7 +460,11 @@
           <t>010501 - 01.05 - Licenciamento ou cessão de direito de uso de programas de computação.</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3353</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
@@ -467,7 +479,11 @@
           <t>010601 - Assessoria e consultoria em informática.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>6102</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
@@ -482,7 +498,11 @@
           <t>010701 - Suporte técnico em informática, inclusive instalação, configuração e manutenção de programas de computação e bancos de dados.</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3353</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
@@ -497,7 +517,11 @@
           <t>042301 - Outros planos de saúde que se cumpram através de serviços de terceiros contratados, credenciados, cooperados ou apenas pagos pelo operador do plano mediante indicação do beneficiário.</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>10668</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
@@ -512,7 +536,11 @@
           <t>070101 - Engenharia e congêneres.</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2998</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
@@ -527,7 +555,11 @@
           <t>070102 - Agronomia e congêneres.</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2998</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
@@ -542,7 +574,11 @@
           <t>070104 - Arquitetura, urbanismo e congêneres.</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2998</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
@@ -557,7 +593,11 @@
           <t>070106 - Paisagismo e congêneres.</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2998</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
@@ -572,7 +612,11 @@
           <t>070201 - Execução, por administração, de obras de construção civil, hidráulica ou elétrica e de outras obras semelhantes, inclusive sondagem, perfuração de poços, escavação, drenagem e irrigação, terraplanagem, pavimentação, concretagem e a instalação e montagem de produtos, peças e equipamentos (exceto o fornecimento de mercadorias produzidas pelo prestador de serviços fora do local da prestação dos serviços, que fica sujeito ao ICMS).</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2998</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
@@ -587,7 +631,11 @@
           <t>070202 - Execução, por empreitada ou subempreitada, de obras de construção civil, hidráulica ou elétrica e de outras obras semelhantes, inclusive sondagem, perfuração de poços, escavação, drenagem e irrigação, terraplanagem, pavimentação, concretagem e a instalação e montagem de produtos, peças e equipamentos (exceto o fornecimento de mercadorias produzidas pelo prestador de serviços fora do local da prestação dos serviços, que fica sujeito ao ICMS).</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2998</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
@@ -602,7 +650,11 @@
           <t>070301 - Elaboração de planos diretores, estudos de viabilidade, estudos organizacionais e outros, relacionados com obras e serviços de engenharia.</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2998</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
@@ -617,7 +669,11 @@
           <t>070302 - Elaboração de anteprojetos, projetos básicos e projetos executivos para trabalhos de engenharia.</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2998</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
@@ -632,7 +688,11 @@
           <t>071101 - Decoração.</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2998</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
@@ -647,7 +707,11 @@
           <t>071901 - Acompanhamento e fiscalização da execução de obras de engenharia, arquitetura e urbanismo.</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2998</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
@@ -662,7 +726,11 @@
           <t>072003 - Levantamentos topográficos e congêneres.</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2998</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
@@ -677,7 +745,11 @@
           <t>080201 - Instrução, treinamento, orientação pedagógica e educacional, avaliação de conhecimentos de qualquer natureza.</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>6102</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
@@ -692,7 +764,11 @@
           <t>100501 - Agenciamento, corretagem ou intermediação de bens móveis ou imóveis, não abrangidos em outros itens</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>4638</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
@@ -707,7 +783,11 @@
           <t>130301 - Fotografia e cinematografia, inclusive revelação, ampliação, cópia, reprodução, trucagem e congêneres.</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2184</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
@@ -722,7 +802,11 @@
           <t>140101 - Lubrificação, limpeza, lustração, revisão, carga e recarga, conserto, restauração, blindagem, manutenção e conservação de máquinas, veículos, aparelhos, equipamentos, motores, elevadores ou de qualquer objeto (exceto peças e partes empregadas, que ficam sujeitas ao ICMS).</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>3066</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
@@ -737,7 +821,11 @@
           <t>140201 - Assistência técnica.</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
@@ -752,7 +840,11 @@
           <t>170101 - Assessoria ou consultoria de qualquer natureza, não contida em outros itens desta lista.</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>6102</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
@@ -767,7 +859,11 @@
           <t>170102 - Análise, exame, pesquisa, coleta, compilação e fornecimento de dados e informações de qualquer natureza, inclusive cadastro e similares.</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2998</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
@@ -782,7 +878,11 @@
           <t>170201 - Datilografia, digitação, estenografia e congêneres.</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
@@ -797,7 +897,11 @@
           <t>170202 - Expediente, secretaria em geral, apoio e infra-estrutura administrativa e congêneres.</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
@@ -812,7 +916,11 @@
           <t>170303 - Planejamento, coordenação, programação ou organização administrativa.</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2998</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
@@ -827,7 +935,11 @@
           <t>170601 - Propaganda e publicidade, inclusive promoção de vendas, planejamento de campanhas ou sistemas de publicidade, elaboração de desenhos, textos e demais materiais publicitários.</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2184</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
@@ -842,7 +954,11 @@
           <t>171201 - Administração em geral, inclusive de bens e negócios de terceiros.</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
@@ -857,7 +973,11 @@
           <t>171401 - Advocacia</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
@@ -872,7 +992,11 @@
           <t>171901 - Contabilidade, inclusive serviços técnicos e auxiliares.</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>3339</t>
+        </is>
+      </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
@@ -887,7 +1011,11 @@
           <t>172001 - Consultoria e assessoria econômica ou financeira.</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>6102</t>
+        </is>
+      </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
@@ -902,7 +1030,11 @@
           <t>230101 - Serviços de programação e comunicação visual e congêneres.</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>3353</t>
+        </is>
+      </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
@@ -917,7 +1049,11 @@
           <t>230102 - Serviços de desenho industrial e congêneres.</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2998</t>
+        </is>
+      </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
@@ -932,7 +1068,11 @@
           <t>320101 - Serviços de desenhos técnicos.</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2998</t>
+        </is>
+      </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
@@ -947,7 +1087,11 @@
           <t>370101 - Serviços de artistas, atletas, modelos e manequins.</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2184</t>
+        </is>
+      </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>

--- a/planos_empresas/plano_empresa_20571.xlsx
+++ b/planos_empresas/plano_empresa_20571.xlsx
@@ -848,7 +848,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>

--- a/planos_empresas/plano_empresa_20571.xlsx
+++ b/planos_empresas/plano_empresa_20571.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1100,6 +1100,111 @@
       </c>
       <c r="E36" t="inlineStr"/>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>040802 - Fisioterapia.</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1939</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>042201 - Planos de medicina de grupo ou individual e convênios para prestação de assistência médica, hospitalar, odontológica e congêneres.</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1939</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>070901 - Varrição, coleta e remoção de lixo, rejeitos e outros resíduos quaisquer.</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>100202 - Agenciamento, corretagem ou intermediação de contratos quais</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>5201</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>100502 - Agenciamento, corretagem ou intermediação de bens móveis ou imóveis realizados no âmbito de Bolsas de Mercadorias e Futuros, por quaisquer meios.</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>5201</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>150103 - Administração de cartão de crédito ou débito e congêneres.</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>5201</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>151401 - Fornecimento, emissão, reemissão de cartão magnético, cartão de crédito, cartão de débito, cartão salário e congêneres.</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>5201</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
